--- a/StructureDefinition-Slutsvar-Dokument-inom-halso--och-sjukvard.xlsx
+++ b/StructureDefinition-Slutsvar-Dokument-inom-halso--och-sjukvard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Slutsvar-Dokument-inom-halso--och-sjukvard.xlsx
+++ b/StructureDefinition-Slutsvar-Dokument-inom-halso--och-sjukvard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Slutsvar : Dokument (inom hälso- och sjukvård)).</t>
+    <t>Svar där samtliga i remissen beställda analyser i och med detta svar är besvarade slutligt, och inga fortsatta analyser pågår.
+Den remissvarsmottagande enheten ska i och med detta inte förvänta sig ytterligare svar. Även efter ett slutsvar finns det möjlighet för utförande enhet att skicka ytterligare svar relaterat till samma remiss.</t>
   </si>
   <si>
     <t>Purpose</t>
